--- a/MySemanticAnalysisSample/Result/TextSimilarityAnalyser (1).xlsx
+++ b/MySemanticAnalysisSample/Result/TextSimilarityAnalyser (1).xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28723"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28801"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC1520E8-CB46-4FB4-ACF5-2CDC58357B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0288E3D8-EEB4-494B-8C45-E11BBFE78F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="best gpt model for word vs word" sheetId="1" r:id="rId1"/>
@@ -14,8 +14,7 @@
     <sheet name="best approach for doc vs word " sheetId="4" r:id="rId4"/>
     <sheet name="Approach for doc vs doc" sheetId="6" r:id="rId5"/>
     <sheet name="best sim metric 4  word vs word" sheetId="5" r:id="rId6"/>
-    <sheet name="best sim metric 4 word vs doc" sheetId="7" r:id="rId7"/>
-    <sheet name="best sim metric 4 doc vs doc" sheetId="8" r:id="rId8"/>
+    <sheet name="Result mode 1" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="195">
   <si>
     <t>Chatgpt embedding models performance comparison</t>
   </si>
@@ -793,7 +792,172 @@
     <t>Similarity metric: Jaccard Similarity</t>
   </si>
   <si>
-    <t>Similarity metric performance comparison for word vs doc</t>
+    <t>Results: Mode 1 Comparing words with words</t>
+  </si>
+  <si>
+    <t>Science &amp; Technology</t>
+  </si>
+  <si>
+    <t>Politics &amp; Leadership</t>
+  </si>
+  <si>
+    <t>Arts &amp; Entertainment</t>
+  </si>
+  <si>
+    <t>Sports</t>
+  </si>
+  <si>
+    <t>Karl Marx</t>
+  </si>
+  <si>
+    <t>Winston Churchill</t>
+  </si>
+  <si>
+    <t>Serena Williams</t>
+  </si>
+  <si>
+    <t>Alan Turing</t>
+  </si>
+  <si>
+    <t>Nikola Tesla</t>
+  </si>
+  <si>
+    <t>Jeff Bezos</t>
+  </si>
+  <si>
+    <t>Michael Phelps</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>Roger Federer</t>
+  </si>
+  <si>
+    <t>Suresh Gopi</t>
+  </si>
+  <si>
+    <t>Mark Zuckerberg</t>
+  </si>
+  <si>
+    <t>Pablo Picasso</t>
+  </si>
+  <si>
+    <t>John F. Kennedy</t>
+  </si>
+  <si>
+    <t>Elon Musk</t>
+  </si>
+  <si>
+    <t>Leonardo da Vinci</t>
+  </si>
+  <si>
+    <t>Aristotle</t>
+  </si>
+  <si>
+    <t>Malala Yousafzai</t>
+  </si>
+  <si>
+    <t>Marie Curie</t>
+  </si>
+  <si>
+    <t>Michael Jordan</t>
+  </si>
+  <si>
+    <t>Charlie Chaplin</t>
+  </si>
+  <si>
+    <t>Actor Vijay</t>
+  </si>
+  <si>
+    <t>Isaac Newton</t>
+  </si>
+  <si>
+    <t>Barack Obama</t>
+  </si>
+  <si>
+    <t>Muhammad Ali</t>
+  </si>
+  <si>
+    <t>Bill Gates</t>
+  </si>
+  <si>
+    <t>Oprah Winfrey</t>
+  </si>
+  <si>
+    <t>Theodore Roosevelt</t>
+  </si>
+  <si>
+    <t>J.K. Rowling</t>
+  </si>
+  <si>
+    <t>Vincent van Gogh</t>
+  </si>
+  <si>
+    <t>Margaret Thatcher</t>
+  </si>
+  <si>
+    <t>Diego Maradona</t>
+  </si>
+  <si>
+    <t>Albert Einstein</t>
+  </si>
+  <si>
+    <t>Thomas Edison</t>
+  </si>
+  <si>
+    <t>Nelson Mandela</t>
+  </si>
+  <si>
+    <t>Usain Bolt</t>
+  </si>
+  <si>
+    <t>Angela Merkel</t>
+  </si>
+  <si>
+    <t>Ludwig van Beethoven</t>
+  </si>
+  <si>
+    <t>Stephen Hawking</t>
+  </si>
+  <si>
+    <t>Walt Disney</t>
+  </si>
+  <si>
+    <t>Confucius</t>
+  </si>
+  <si>
+    <t>Tom Brady</t>
+  </si>
+  <si>
+    <t>Mahatma Gandhi</t>
+  </si>
+  <si>
+    <t>Galileo Galilei</t>
+  </si>
+  <si>
+    <t>Wolfgang Amadeus Mozart</t>
+  </si>
+  <si>
+    <t>Abraham Lincoln</t>
+  </si>
+  <si>
+    <t>Steve Jobs</t>
+  </si>
+  <si>
+    <t>Marilyn Monroe</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo</t>
+  </si>
+  <si>
+    <t>Charles Darwin</t>
+  </si>
+  <si>
+    <t>Lionel Messi</t>
+  </si>
+  <si>
+    <t>Sigmund Freud</t>
   </si>
 </sst>
 </file>
@@ -2075,37 +2239,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -2203,9 +2337,6 @@
               <c:f>'best approach for doc vs word '!$D$26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Global Warming</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2251,24 +2382,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>0.1286399</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.51498436999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13860528</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13973661000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9.9243744999999994E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.54025877</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2812,45 +2925,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.21965597289049013"/>
-          <c:y val="2.6754998401403791E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -3255,9 +3330,6 @@
               <c:f>'best approach for doc vs word '!$D$48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Global Warming</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -3303,24 +3375,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>0.12767435999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.52346349999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.14210755</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14456891999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.10256305</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.54122983999999996</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4907,9 +4961,6 @@
               <c:f>'best approach for doc vs word '!$D$126</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Global Warming</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -4955,24 +5006,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>0.14754201</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.56830895000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.18156943</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.17488687999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.527121E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.53402406000000002</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5516,37 +5549,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -10329,6 +10332,1665 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="109908999"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Result mode 1'!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Science &amp; Technology</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Result mode 1'!$B$11:$B$61</c:f>
+              <c:strCache>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>Karl Marx</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Winston Churchill</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Serena Williams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alan Turing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nikola Tesla</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jeff Bezos</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Michael Phelps</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>William Shakespeare</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Roger Federer</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Suresh Gopi</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Mark Zuckerberg</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pablo Picasso</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>John F. Kennedy</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Elon Musk</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Leonardo da Vinci</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Aristotle</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Malala Yousafzai</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Marie Curie</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Michael Jordan</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Charlie Chaplin</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Actor Vijay</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Isaac Newton</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Barack Obama</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Muhammad Ali</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Bill Gates</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Oprah Winfrey</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Theodore Roosevelt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>J.K. Rowling</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Vincent van Gogh</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Margaret Thatcher</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Diego Maradona</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Albert Einstein</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Thomas Edison</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Nelson Mandela</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Usain Bolt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Angela Merkel</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ludwig van Beethoven</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Stephen Hawking</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Walt Disney</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Confucius</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Tom Brady</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Mahatma Gandhi</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Galileo Galilei</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Wolfgang Amadeus Mozart</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Abraham Lincoln</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Steve Jobs</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Marilyn Monroe</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Cristiano Ronaldo</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Charles Darwin</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Lionel Messi</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Sigmund Freud</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Result mode 1'!$C$11:$C$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.182</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.24299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.19400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.185</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.22900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.253</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.214</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.25700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.252</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.128</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.13400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.25900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.13200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.14599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.25600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CA83-4EEF-9F4D-473D695302D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Result mode 1'!$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Politics &amp; Leadership</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Result mode 1'!$B$11:$B$61</c:f>
+              <c:strCache>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>Karl Marx</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Winston Churchill</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Serena Williams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alan Turing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nikola Tesla</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jeff Bezos</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Michael Phelps</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>William Shakespeare</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Roger Federer</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Suresh Gopi</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Mark Zuckerberg</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pablo Picasso</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>John F. Kennedy</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Elon Musk</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Leonardo da Vinci</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Aristotle</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Malala Yousafzai</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Marie Curie</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Michael Jordan</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Charlie Chaplin</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Actor Vijay</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Isaac Newton</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Barack Obama</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Muhammad Ali</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Bill Gates</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Oprah Winfrey</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Theodore Roosevelt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>J.K. Rowling</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Vincent van Gogh</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Margaret Thatcher</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Diego Maradona</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Albert Einstein</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Thomas Edison</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Nelson Mandela</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Usain Bolt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Angela Merkel</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ludwig van Beethoven</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Stephen Hawking</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Walt Disney</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Confucius</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Tom Brady</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Mahatma Gandhi</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Galileo Galilei</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Wolfgang Amadeus Mozart</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Abraham Lincoln</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Steve Jobs</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Marilyn Monroe</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Cristiano Ronaldo</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Charles Darwin</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Lionel Messi</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Sigmund Freud</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Result mode 1'!$D$11:$D$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>0.19700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.151</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.153</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.124</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.20699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.127</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.27500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.187</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.23899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.185</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.107</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.154</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.151</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.115</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.29699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.184</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.23599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.26400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.27200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.16600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.26200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.27700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.121</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.16800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.23400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.20200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.22600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.23200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.20300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.14099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.14799999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-CA83-4EEF-9F4D-473D695302D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Result mode 1'!$E$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arts &amp; Entertainment</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Result mode 1'!$B$11:$B$61</c:f>
+              <c:strCache>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>Karl Marx</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Winston Churchill</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Serena Williams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alan Turing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nikola Tesla</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jeff Bezos</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Michael Phelps</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>William Shakespeare</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Roger Federer</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Suresh Gopi</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Mark Zuckerberg</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pablo Picasso</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>John F. Kennedy</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Elon Musk</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Leonardo da Vinci</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Aristotle</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Malala Yousafzai</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Marie Curie</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Michael Jordan</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Charlie Chaplin</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Actor Vijay</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Isaac Newton</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Barack Obama</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Muhammad Ali</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Bill Gates</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Oprah Winfrey</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Theodore Roosevelt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>J.K. Rowling</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Vincent van Gogh</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Margaret Thatcher</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Diego Maradona</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Albert Einstein</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Thomas Edison</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Nelson Mandela</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Usain Bolt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Angela Merkel</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ludwig van Beethoven</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Stephen Hawking</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Walt Disney</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Confucius</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Tom Brady</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Mahatma Gandhi</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Galileo Galilei</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Wolfgang Amadeus Mozart</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Abraham Lincoln</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Steve Jobs</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Marilyn Monroe</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Cristiano Ronaldo</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Charles Darwin</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Lionel Messi</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Sigmund Freud</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Result mode 1'!$E$11:$E$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>0.114</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.112</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.153</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.127</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.20499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.161</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.129</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.14499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.156</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.23100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.111</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.14199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.19400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.17699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.111</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.16800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.159</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.222</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.17399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.16300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.17199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.16900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.13600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.14899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.245</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.17399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.17899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.189</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.14499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.11600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-CA83-4EEF-9F4D-473D695302D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Result mode 1'!$F$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sports</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Result mode 1'!$B$11:$B$61</c:f>
+              <c:strCache>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>Karl Marx</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Winston Churchill</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Serena Williams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alan Turing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nikola Tesla</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jeff Bezos</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Michael Phelps</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>William Shakespeare</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Roger Federer</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Suresh Gopi</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Mark Zuckerberg</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pablo Picasso</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>John F. Kennedy</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Elon Musk</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Leonardo da Vinci</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Aristotle</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Malala Yousafzai</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Marie Curie</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Michael Jordan</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Charlie Chaplin</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Actor Vijay</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Isaac Newton</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Barack Obama</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Muhammad Ali</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Bill Gates</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Oprah Winfrey</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Theodore Roosevelt</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>J.K. Rowling</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Vincent van Gogh</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Margaret Thatcher</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Diego Maradona</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Albert Einstein</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Thomas Edison</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Nelson Mandela</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Usain Bolt</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Angela Merkel</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ludwig van Beethoven</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Stephen Hawking</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Walt Disney</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Confucius</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Tom Brady</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Mahatma Gandhi</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Galileo Galilei</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Wolfgang Amadeus Mozart</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Abraham Lincoln</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Steve Jobs</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Marilyn Monroe</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Cristiano Ronaldo</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Charles Darwin</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Lionel Messi</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Sigmund Freud</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Result mode 1'!$F$11:$F$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28899999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.28199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.16300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.251</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.14799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.107</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.14299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.158</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.13600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.29199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.13700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.153</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.23699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.154</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.14199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.151</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.23200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.157</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.314</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.158</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.14499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.14399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.315</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.13600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.6999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.151</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.248</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.156</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.223</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-CA83-4EEF-9F4D-473D695302D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1751802887"/>
+        <c:axId val="1751804935"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1751802887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1751804935"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1751804935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1751802887"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14804,6 +16466,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors26.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -23636,6 +25338,509 @@
 </file>
 
 <file path=xl/charts/style25.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style26.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -28146,8 +30351,8 @@
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -28652,6 +30857,50 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>314325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C950B5-3CE9-9AC9-B2AD-2F4AE7A6B3D2}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3961A06F-34A7-AE6C-EBEB-96E425F05810}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -31318,9 +33567,7 @@
       <c r="C26" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>78</v>
-      </c>
+      <c r="D26" s="10"/>
       <c r="T26" s="1"/>
       <c r="AG26" s="1"/>
       <c r="AM26" s="1"/>
@@ -31343,9 +33590,7 @@
       <c r="C27" s="1">
         <v>0.44052910000000001</v>
       </c>
-      <c r="D27" s="1">
-        <v>0.1286399</v>
-      </c>
+      <c r="D27" s="1"/>
       <c r="T27" s="1"/>
       <c r="AG27" s="1"/>
       <c r="AM27" s="1"/>
@@ -31368,9 +33613,6 @@
       <c r="C28" s="1">
         <v>0.33757029999999999</v>
       </c>
-      <c r="D28">
-        <v>0.51498436999999997</v>
-      </c>
       <c r="T28" s="1"/>
       <c r="AG28" s="1"/>
       <c r="AM28" s="1"/>
@@ -31393,9 +33635,7 @@
       <c r="C29" s="1">
         <v>0.31332618000000001</v>
       </c>
-      <c r="D29" s="1">
-        <v>0.13860528</v>
-      </c>
+      <c r="D29" s="1"/>
       <c r="T29" s="1"/>
       <c r="AG29" s="1"/>
       <c r="AM29" s="1"/>
@@ -31418,9 +33658,7 @@
       <c r="C30" s="1">
         <v>0.31247002000000001</v>
       </c>
-      <c r="D30" s="1">
-        <v>0.13973661000000001</v>
-      </c>
+      <c r="D30" s="1"/>
       <c r="T30" s="1"/>
       <c r="AG30" s="1"/>
       <c r="AM30" s="1"/>
@@ -31443,9 +33681,7 @@
       <c r="C31" s="1">
         <v>0.185862</v>
       </c>
-      <c r="D31" s="1">
-        <v>9.9243744999999994E-2</v>
-      </c>
+      <c r="D31" s="1"/>
       <c r="T31" s="1"/>
       <c r="AG31" s="1"/>
       <c r="AM31" s="1"/>
@@ -31467,9 +33703,6 @@
       </c>
       <c r="C32" s="1">
         <v>9.236055E-2</v>
-      </c>
-      <c r="D32">
-        <v>0.54025877</v>
       </c>
       <c r="T32" s="1"/>
       <c r="AG32" s="1"/>
@@ -31654,15 +33887,13 @@
       <c r="AH47" s="39"/>
       <c r="AI47" s="39"/>
     </row>
-    <row r="48" spans="1:35" ht="29.25">
+    <row r="48" spans="1:35" ht="18.75">
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="20" t="s">
-        <v>78</v>
-      </c>
+      <c r="D48" s="20"/>
       <c r="E48" s="39"/>
       <c r="F48" s="39"/>
       <c r="G48" s="39"/>
@@ -31705,9 +33936,7 @@
       <c r="C49" s="20">
         <v>0.44138524000000001</v>
       </c>
-      <c r="D49" s="20">
-        <v>0.12767435999999999</v>
-      </c>
+      <c r="D49" s="20"/>
       <c r="E49" s="39"/>
       <c r="F49" s="39"/>
       <c r="G49" s="39"/>
@@ -31748,9 +33977,7 @@
       <c r="C50" s="20">
         <v>0.33425411999999999</v>
       </c>
-      <c r="D50" s="20">
-        <v>0.52346349999999997</v>
-      </c>
+      <c r="D50" s="20"/>
       <c r="E50" s="39"/>
       <c r="F50" s="39"/>
       <c r="G50" s="39"/>
@@ -31791,9 +34018,7 @@
       <c r="C51" s="20">
         <v>0.31419357999999997</v>
       </c>
-      <c r="D51" s="20">
-        <v>0.14210755</v>
-      </c>
+      <c r="D51" s="20"/>
       <c r="E51" s="39"/>
       <c r="I51" s="39"/>
       <c r="J51" s="39"/>
@@ -31831,9 +34056,7 @@
       <c r="C52" s="20">
         <v>0.31432622999999998</v>
       </c>
-      <c r="D52" s="20">
-        <v>0.14456891999999999</v>
-      </c>
+      <c r="D52" s="20"/>
       <c r="E52" s="39"/>
       <c r="I52" s="39"/>
       <c r="J52" s="39"/>
@@ -31871,9 +34094,7 @@
       <c r="C53" s="20">
         <v>0.18780669999999999</v>
       </c>
-      <c r="D53" s="20">
-        <v>0.10256305</v>
-      </c>
+      <c r="D53" s="20"/>
       <c r="E53" s="39"/>
       <c r="F53" s="39"/>
       <c r="G53" s="39"/>
@@ -31914,9 +34135,7 @@
       <c r="C54" s="20">
         <v>0.10135274</v>
       </c>
-      <c r="D54" s="20">
-        <v>0.54122983999999996</v>
-      </c>
+      <c r="D54" s="20"/>
       <c r="E54" s="39"/>
       <c r="F54" s="39"/>
       <c r="G54" s="39"/>
@@ -35565,9 +37784,7 @@
       <c r="C126" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D126" s="20" t="s">
-        <v>78</v>
-      </c>
+      <c r="D126" s="20"/>
       <c r="E126" s="39"/>
       <c r="F126" s="39"/>
       <c r="G126" s="39"/>
@@ -35639,9 +37856,7 @@
       <c r="C127" s="20">
         <v>0.44614163000000001</v>
       </c>
-      <c r="D127" s="20">
-        <v>0.14754201</v>
-      </c>
+      <c r="D127" s="20"/>
       <c r="E127" s="39"/>
       <c r="F127" s="39"/>
       <c r="G127" s="39"/>
@@ -35713,9 +37928,7 @@
       <c r="C128" s="20">
         <v>0.39114189999999999</v>
       </c>
-      <c r="D128" s="20">
-        <v>0.56830895000000003</v>
-      </c>
+      <c r="D128" s="20"/>
       <c r="E128" s="39"/>
       <c r="F128" s="39"/>
       <c r="G128" s="39"/>
@@ -35787,9 +38000,7 @@
       <c r="C129" s="20">
         <v>0.31431049999999999</v>
       </c>
-      <c r="D129" s="20">
-        <v>0.18156943</v>
-      </c>
+      <c r="D129" s="20"/>
       <c r="E129" s="39"/>
       <c r="F129" s="39"/>
       <c r="G129" s="39"/>
@@ -35861,9 +38072,7 @@
       <c r="C130" s="20">
         <v>0.30900929999999999</v>
       </c>
-      <c r="D130" s="20">
-        <v>0.17488687999999999</v>
-      </c>
+      <c r="D130" s="20"/>
       <c r="E130" s="39"/>
       <c r="F130" s="39"/>
       <c r="G130" s="39"/>
@@ -35935,9 +38144,7 @@
       <c r="C131" s="20">
         <v>0.18363305999999999</v>
       </c>
-      <c r="D131" s="20">
-        <v>8.527121E-2</v>
-      </c>
+      <c r="D131" s="20"/>
       <c r="E131" s="39"/>
       <c r="F131" s="39"/>
       <c r="G131" s="39"/>
@@ -36009,9 +38216,7 @@
       <c r="C132" s="20">
         <v>9.1521025000000006E-2</v>
       </c>
-      <c r="D132" s="20">
-        <v>0.53402406000000002</v>
-      </c>
+      <c r="D132" s="20"/>
       <c r="E132" s="39"/>
       <c r="F132" s="39"/>
       <c r="G132" s="39"/>
@@ -39267,8 +41472,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EAAABD-8A8F-442A-9A71-723A46353F12}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" s="63" customFormat="1" ht="26.25" customHeight="1">
       <c r="A1" s="63" t="s">
@@ -39276,9 +41488,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="43" t="s">
-        <v>134</v>
-      </c>
+      <c r="A2" s="43"/>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
       <c r="D2" s="43"/>
@@ -39286,9 +41496,7 @@
       <c r="F2" s="43"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="43" t="s">
-        <v>54</v>
-      </c>
+      <c r="A3" s="43"/>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
       <c r="D3" s="43"/>
@@ -39302,6 +41510,890 @@
       <c r="D9" s="63"/>
       <c r="E9" s="63"/>
       <c r="F9" s="63"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11">
+        <v>0.105</v>
+      </c>
+      <c r="D11">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="E11">
+        <v>0.114</v>
+      </c>
+      <c r="F11">
+        <v>0.13800000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="D12">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="E12">
+        <v>0.112</v>
+      </c>
+      <c r="F12">
+        <v>0.14099999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13">
+        <v>0.105</v>
+      </c>
+      <c r="D13">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="F13">
+        <v>0.28899999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="D14">
+        <v>0.105</v>
+      </c>
+      <c r="E14">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="F14">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="D15">
+        <v>9.4E-2</v>
+      </c>
+      <c r="E15">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="F15">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16">
+        <v>0.18</v>
+      </c>
+      <c r="D16">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="E16">
+        <v>0.153</v>
+      </c>
+      <c r="F16">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17">
+        <v>0.105</v>
+      </c>
+      <c r="D17">
+        <v>0.151</v>
+      </c>
+      <c r="E17">
+        <v>0.127</v>
+      </c>
+      <c r="F17">
+        <v>0.28199999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D18">
+        <v>0.153</v>
+      </c>
+      <c r="E18">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="F18">
+        <v>0.16300000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="D19">
+        <v>0.124</v>
+      </c>
+      <c r="E19">
+        <v>0.161</v>
+      </c>
+      <c r="F19">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20">
+        <v>0.123</v>
+      </c>
+      <c r="D20">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="E20">
+        <v>0.129</v>
+      </c>
+      <c r="F20">
+        <v>0.16200000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21">
+        <v>0.182</v>
+      </c>
+      <c r="D21">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="E21">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="F21">
+        <v>0.14799999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="D22">
+        <v>0.127</v>
+      </c>
+      <c r="E22">
+        <v>0.2</v>
+      </c>
+      <c r="F22">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="D23">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="E23">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="F23">
+        <v>0.14299999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D24">
+        <v>0.187</v>
+      </c>
+      <c r="E24">
+        <v>0.156</v>
+      </c>
+      <c r="F24">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="E25">
+        <v>0.19</v>
+      </c>
+      <c r="F25">
+        <v>0.13900000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26">
+        <v>0.185</v>
+      </c>
+      <c r="D26">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="E26">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="F26">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D27">
+        <v>0.185</v>
+      </c>
+      <c r="E27">
+        <v>0.111</v>
+      </c>
+      <c r="F27">
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="D28">
+        <v>0.107</v>
+      </c>
+      <c r="E28">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="F28">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="D29">
+        <v>0.154</v>
+      </c>
+      <c r="E29">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="F29">
+        <v>0.29199999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="D30">
+        <v>0.151</v>
+      </c>
+      <c r="E30">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="F30">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31">
+        <v>0.109</v>
+      </c>
+      <c r="D31">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="E31">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="F31">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32">
+        <v>0.253</v>
+      </c>
+      <c r="D32">
+        <v>0.115</v>
+      </c>
+      <c r="E32">
+        <v>0.111</v>
+      </c>
+      <c r="F32">
+        <v>0.13900000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="D33">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="E33">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="F33">
+        <v>0.13800000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="D34">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="E34">
+        <v>0.159</v>
+      </c>
+      <c r="F34">
+        <v>0.23699999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35">
+        <v>0.214</v>
+      </c>
+      <c r="D35">
+        <v>0.184</v>
+      </c>
+      <c r="E35">
+        <v>0.125</v>
+      </c>
+      <c r="F35">
+        <v>0.14699999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36">
+        <v>0.11</v>
+      </c>
+      <c r="D36">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="E36">
+        <v>0.222</v>
+      </c>
+      <c r="F36">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37">
+        <v>0.12</v>
+      </c>
+      <c r="D37">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="E37">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F37">
+        <v>0.14199999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="D38">
+        <v>0.17</v>
+      </c>
+      <c r="E38">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="F38">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D39">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="E39">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="F39">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" t="s">
+        <v>173</v>
+      </c>
+      <c r="C40">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="D40">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="E40">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="F40">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="D41">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="E41">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F41">
+        <v>0.23200000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="D42">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="E42">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="F42">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" t="s">
+        <v>176</v>
+      </c>
+      <c r="C43">
+        <v>0.252</v>
+      </c>
+      <c r="D43">
+        <v>0.123</v>
+      </c>
+      <c r="E43">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="F43">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C44">
+        <v>0.128</v>
+      </c>
+      <c r="D44">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="E44">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="F44">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="D45">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="E45">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="F45">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="D46">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="E46">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F46">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" t="s">
+        <v>180</v>
+      </c>
+      <c r="C47">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="D47">
+        <v>0.121</v>
+      </c>
+      <c r="E47">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="F47">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="D48">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="E48">
+        <v>0.123</v>
+      </c>
+      <c r="F48">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" t="s">
+        <v>182</v>
+      </c>
+      <c r="C49">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="D49">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="E49">
+        <v>0.245</v>
+      </c>
+      <c r="F49">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50">
+        <v>0.108</v>
+      </c>
+      <c r="D50">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="E50">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="F50">
+        <v>0.14399999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="D51">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="E51">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="F51">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="D52">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="E52">
+        <v>9.4E-2</v>
+      </c>
+      <c r="F52">
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="D53">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="E53">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F53">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" t="s">
+        <v>187</v>
+      </c>
+      <c r="C54">
+        <v>7.8E-2</v>
+      </c>
+      <c r="D54">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="E54">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="F54">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" t="s">
+        <v>188</v>
+      </c>
+      <c r="C55">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D55">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="E55">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="F55">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" t="s">
+        <v>189</v>
+      </c>
+      <c r="C56">
+        <v>0.24</v>
+      </c>
+      <c r="D56">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="E56">
+        <v>0.18</v>
+      </c>
+      <c r="F56">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" t="s">
+        <v>190</v>
+      </c>
+      <c r="C57">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="D57">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="E57">
+        <v>0.189</v>
+      </c>
+      <c r="F57">
+        <v>0.13900000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C58">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="D58">
+        <v>0.12</v>
+      </c>
+      <c r="E58">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="F58">
+        <v>0.248</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" t="s">
+        <v>192</v>
+      </c>
+      <c r="C59">
+        <v>0.19</v>
+      </c>
+      <c r="D59">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="E59">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="F59">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C60">
+        <v>0.125</v>
+      </c>
+      <c r="D60">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="E60">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="F60">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="D61">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="E61">
+        <v>0.13</v>
+      </c>
+      <c r="F61">
+        <v>0.13300000000000001</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -39311,14 +42403,6 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F485B6-F0F1-4B02-8E72-6599557270F5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>